--- a/Sitios_Colecta/Colecta.xlsx
+++ b/Sitios_Colecta/Colecta.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/90fd6f18a721c321/Documentos/19_Migraciones/redtopolgicamagdalenashpfiles/Sitios_Colecta/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/90fd6f18a721c321/Documentos/19_Migraciones/red_topolgica_magdalena_shp_files/Sitios_Colecta/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_F25DC773A252ABDACC1048B2D19F79F45ADE58F8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E775AFF6-F660-4627-B853-665082C3D362}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_F25DC773A252ABDACC1048B2D19F79F45ADE58F8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3B8FFC82-FB2A-4BD6-A995-0CF7EEB1A479}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -513,6 +513,7 @@
   <dimension ref="A1:G187"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="2" width="42.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="32.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
